--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -386,16 +386,16 @@
         <v>23386</v>
       </c>
       <c r="B2">
-        <v>61</v>
+        <v>1014</v>
       </c>
       <c r="C2">
-        <v>0.26</v>
+        <v>4.34</v>
       </c>
       <c r="D2">
-        <v>23325</v>
+        <v>22372</v>
       </c>
       <c r="E2">
-        <v>99.73999999999999</v>
+        <v>95.66</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23386</v>
+        <v>23957</v>
       </c>
       <c r="B2">
-        <v>1014</v>
+        <v>800</v>
       </c>
       <c r="C2">
-        <v>4.34</v>
+        <v>3.34</v>
       </c>
       <c r="D2">
-        <v>22372</v>
+        <v>23157</v>
       </c>
       <c r="E2">
-        <v>95.66</v>
+        <v>96.66</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23957</v>
+        <v>23856</v>
       </c>
       <c r="B2">
-        <v>800</v>
+        <v>723</v>
       </c>
       <c r="C2">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="D2">
-        <v>23157</v>
+        <v>23133</v>
       </c>
       <c r="E2">
-        <v>96.66</v>
+        <v>96.97</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -386,16 +386,16 @@
         <v>23856</v>
       </c>
       <c r="B2">
-        <v>723</v>
+        <v>631</v>
       </c>
       <c r="C2">
-        <v>3.03</v>
+        <v>2.65</v>
       </c>
       <c r="D2">
-        <v>23133</v>
+        <v>23225</v>
       </c>
       <c r="E2">
-        <v>96.97</v>
+        <v>97.34999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23856</v>
+        <v>23956</v>
       </c>
       <c r="B2">
-        <v>631</v>
+        <v>732</v>
       </c>
       <c r="C2">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="D2">
-        <v>23225</v>
+        <v>23224</v>
       </c>
       <c r="E2">
-        <v>97.34999999999999</v>
+        <v>96.94</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23956</v>
+        <v>17705</v>
       </c>
       <c r="B2">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C2">
-        <v>3.06</v>
+        <v>4.11</v>
       </c>
       <c r="D2">
-        <v>23224</v>
+        <v>16978</v>
       </c>
       <c r="E2">
-        <v>96.94</v>
+        <v>95.89</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -383,19 +383,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>17705</v>
+        <v>22900</v>
       </c>
       <c r="B2">
-        <v>727</v>
+        <v>621</v>
       </c>
       <c r="C2">
-        <v>4.11</v>
+        <v>2.71</v>
       </c>
       <c r="D2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="E2">
-        <v>95.89</v>
+        <v>97.29000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
+++ b/OMOP Analysis/Results/cohort_summary_OMOP.xlsx
@@ -386,16 +386,16 @@
         <v>22900</v>
       </c>
       <c r="B2">
-        <v>621</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>22279</v>
+        <v>22900</v>
       </c>
       <c r="E2">
-        <v>97.29000000000001</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
